--- a/DATA/generated_random_demand_scenarios.xlsx
+++ b/DATA/generated_random_demand_scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="4_{2D12AA8F-2E40-44A7-809E-99A656943D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{971EB046-5F90-4B29-9230-5128C5EC4573}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="4_{2D12AA8F-2E40-44A7-809E-99A656943D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B3B9901-D6A6-4F41-985E-EA7BE291393B}"/>
   <bookViews>
     <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="37" activeTab="49" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
@@ -64,17 +64,28 @@
     <sheet name="Scenario_49" sheetId="49" r:id="rId49"/>
     <sheet name="Scenario_50" sheetId="50" r:id="rId50"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="26">
   <si>
     <t>Vaccine</t>
   </si>
@@ -144,14 +155,30 @@
   <si>
     <t>PCV</t>
   </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Scaled Capacity</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -175,14 +202,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{D1DFE6DD-C7C5-4575-BB1E-E8B6F37BED34}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -195,6 +225,1186 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Updated Demand v Capacity - Antigen</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Scenario_50!$G$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Demand</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Scenario_50!$F$29:$F$40</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Hib</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Polio</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>HPV</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Scenario_50!$G$29:$G$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>392433645.50669652</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26202387.718242884</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>378800029.55425608</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>707933804.44231188</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>606585491.26533163</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>333801996.37829506</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>393195221.63544863</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>300189881.13855594</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>651240059.78908348</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29003959.642525043</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>190555609.21358225</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>223612967.86375159</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9E7F-4022-B766-74C9B2DA4614}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Scenario_50!$H$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Capacity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Scenario_50!$F$29:$F$40</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Hib</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Polio</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>HPV</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Scenario_50!$H$29:$H$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>264193987.60999981</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23500755.779999979</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>225259255.1799998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450649755.54799962</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>462199401.72799963</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>260776685.13600001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>203995434.479</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>200773991.76300001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>435182360.99999928</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>64210185.419999987</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>138970173.69999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>148936259.0999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9E7F-4022-B766-74C9B2DA4614}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Scenario_50!$I$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Scaled Capacity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Scenario_50!$I$29:$I$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>369871582.65399969</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32901058.091999967</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>315362957.25199968</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>630909657.7671994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>647079162.41919947</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>365087359.1904</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>285593608.27059996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>281083588.46820003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>609255305.3999989</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89894259.58799997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>194558243.17999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>208510762.73999956</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9E7F-4022-B766-74C9B2DA4614}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="268553471"/>
+        <c:axId val="278034783"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="268553471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="278034783"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="278034783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="268553471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>749299</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>739774</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C14EA4F2-733E-B905-0212-2D6BC9B78C2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21419,8 +22629,12 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A0D296-FA1C-4AEE-BF0F-3977CFF98F2E}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -21877,8 +23091,239 @@
         <v>571232114.87386942</v>
       </c>
     </row>
+    <row r="28" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>392433645.50669652</v>
+      </c>
+      <c r="H29" s="1">
+        <v>264193987.60999981</v>
+      </c>
+      <c r="I29">
+        <f>H29*1.4</f>
+        <v>369871582.65399969</v>
+      </c>
+    </row>
+    <row r="30" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30">
+        <v>26202387.718242884</v>
+      </c>
+      <c r="H30" s="1">
+        <v>23500755.779999979</v>
+      </c>
+      <c r="I30">
+        <f t="shared" ref="I30:I40" si="0">H30*1.4</f>
+        <v>32901058.091999967</v>
+      </c>
+    </row>
+    <row r="31" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>378800029.55425608</v>
+      </c>
+      <c r="H31" s="1">
+        <v>225259255.1799998</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>315362957.25199968</v>
+      </c>
+    </row>
+    <row r="32" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32">
+        <v>707933804.44231188</v>
+      </c>
+      <c r="H32" s="1">
+        <v>450649755.54799962</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>630909657.7671994</v>
+      </c>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>606585491.26533163</v>
+      </c>
+      <c r="H33" s="1">
+        <v>462199401.72799963</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>647079162.41919947</v>
+      </c>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>333801996.37829506</v>
+      </c>
+      <c r="H34" s="1">
+        <v>260776685.13600001</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>365087359.1904</v>
+      </c>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35">
+        <v>393195221.63544863</v>
+      </c>
+      <c r="H35" s="1">
+        <v>203995434.479</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="0"/>
+        <v>285593608.27059996</v>
+      </c>
+    </row>
+    <row r="36" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36">
+        <v>300189881.13855594</v>
+      </c>
+      <c r="H36" s="1">
+        <v>200773991.76300001</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>281083588.46820003</v>
+      </c>
+    </row>
+    <row r="37" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37">
+        <v>651240059.78908348</v>
+      </c>
+      <c r="H37" s="1">
+        <v>435182360.99999928</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="0"/>
+        <v>609255305.3999989</v>
+      </c>
+    </row>
+    <row r="38" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38">
+        <v>29003959.642525043</v>
+      </c>
+      <c r="H38" s="1">
+        <v>64210185.419999987</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="0"/>
+        <v>89894259.58799997</v>
+      </c>
+    </row>
+    <row r="39" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39">
+        <v>190555609.21358225</v>
+      </c>
+      <c r="H39" s="1">
+        <v>138970173.69999999</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="0"/>
+        <v>194558243.17999998</v>
+      </c>
+    </row>
+    <row r="40" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40">
+        <v>223612967.86375159</v>
+      </c>
+      <c r="H40" s="1">
+        <v>148936259.0999997</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="0"/>
+        <v>208510762.73999956</v>
+      </c>
+    </row>
+    <row r="47" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F58" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
